--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2018_tarapaca.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2018_tarapaca.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:35</t>
+    <t xml:space="preserve">2026-10-05 01:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>854856.31</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>843044.75</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>843187.12</v>
+        <v>843187.13</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>802344.94</v>
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>933303.12</v>
+        <v>933303.13</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>876986.31</v>
@@ -836,7 +836,7 @@
         <v>878153.88</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +888,7 @@
         <v>20</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>892274.62</v>
+        <v>892274.63</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>850702.38</v>
@@ -899,7 +899,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>884528.12</v>
+        <v>884528.13</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>852706.38</v>
@@ -910,10 +910,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>878554.62</v>
+        <v>878554.63</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -998,10 +998,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>925576.62</v>
+        <v>925576.63</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>898652.75</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1075,7 +1075,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>931354.62</v>
+        <v>931354.63</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>900212.25</v>
@@ -1166,7 +1166,7 @@
         <v>965942.94</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1229,7 +1229,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1025128.12</v>
+        <v>1025128.13</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>990892.69</v>
@@ -1240,7 +1240,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1002756.12</v>
+        <v>1002756.13</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>984727.69</v>
@@ -1251,7 +1251,7 @@
         <v>53</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1060570.62</v>
+        <v>1060570.63</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>1019749.94</v>
@@ -1287,7 +1287,7 @@
         <v>1082164.75</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>1089287.88</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1306,7 +1306,7 @@
         <v>58</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1092854.62</v>
+        <v>1092854.63</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>1074313.38</v>
@@ -1342,7 +1342,7 @@
         <v>1121291.38</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1361,10 +1361,10 @@
         <v>63</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1205748.62</v>
+        <v>1205748.63</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1394,7 +1394,7 @@
         <v>66</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>1203851.12</v>
+        <v>1203851.13</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>1168289.25</v>
@@ -1419,7 +1419,7 @@
         <v>1213442</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1438,7 +1438,7 @@
         <v>70</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1208604.62</v>
+        <v>1208604.63</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>1186515.5</v>
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1281590.12</v>
+        <v>1281590.13</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>1246393.5</v>
@@ -1460,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1239663.12</v>
+        <v>1239663.13</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>1202545</v>
@@ -1482,7 +1482,7 @@
         <v>74</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>1327918.62</v>
+        <v>1327918.63</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>1284570.75</v>
@@ -1518,7 +1518,7 @@
         <v>1265392.75</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1548,10 +1548,10 @@
         <v>80</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1280176.12</v>
+        <v>1280176.13</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1559,10 +1559,10 @@
         <v>81</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>1313260.62</v>
+        <v>1313260.63</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1367577.5</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
@@ -1592,7 +1592,7 @@
         <v>84</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>1317296.62</v>
+        <v>1317296.63</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>1278548.38</v>
